--- a/ai/data/history/DotNetJobs_14082026.xlsx
+++ b/ai/data/history/DotNetJobs_14082026.xlsx
@@ -54,7 +54,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,12 +71,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FA"/>
-        <bgColor rgb="00F2F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,15 +131,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -513,14 +498,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="53" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -535,7 +520,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: August 14, 2026 - 12:11 AM | Total Jobs: 2</t>
+          <t>Report Generated: August 14, 2026 - 11:54 PM | Total Jobs: 1</t>
         </is>
       </c>
     </row>
@@ -583,7 +568,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -593,64 +578,28 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Manufacturing Test</t>
+          <t>Embedded Software Engineer, Intelligence Systems</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Bellevue, Washington, United States</t>
+          <t>Santa Ana, California, United States</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>4 years, 8 years</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5161503007?gh_jid=5161503007</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Ripple</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Staff Full-Stack Software Engineer (.NET &amp; Azure)</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Chicago, Illinois, United States</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>8 years, 40 years</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>https://ripple.com/careers/all-jobs/job/7896103?gh_jid=7896103</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5212828007?gh_jid=5212828007</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
